--- a/results_cnn_subnetwork_evaluation/baselines/cnn_evaluation(stress_test)_pcc_origin.xlsx
+++ b/results_cnn_subnetwork_evaluation/baselines/cnn_evaluation(stress_test)_pcc_origin.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\modeling_vce_dm_gaussian\results_cnn_subnetwork_evaluation\pcc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation\baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6A2BFB-56F6-4E6A-B23B-B8D1DE03BAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
